--- a/inst/extdata/wb_projects_gov_sar.xlsx
+++ b/inst/extdata/wb_projects_gov_sar.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -85,24 +85,6 @@
   </si>
   <si>
     <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">P515116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bangladesh Strengthening Governance and Institutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To support strengthening of governance and institutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">People's Republic of Bangladesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P515116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nataliya Biletska (ADM)</t>
   </si>
 </sst>
 </file>
@@ -514,13 +496,13 @@
     <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="36.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="42.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="18.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="7.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="23.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
@@ -608,44 +590,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/inst/extdata/wb_projects_gov_sar.xlsx
+++ b/inst/extdata/wb_projects_gov_sar.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -52,6 +52,18 @@
   </si>
   <si>
     <t xml:space="preserve">commitment_amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_pfm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_procurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_public_admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_env_social</t>
   </si>
   <si>
     <t xml:space="preserve">comments</t>
@@ -434,7 +446,11 @@
     <col min="11" max="11" width="3.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,6 +495,18 @@
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -505,7 +533,11 @@
     <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -551,43 +583,67 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2028</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>23</v>
+      <c r="N2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/wb_projects_gov_sar.xlsx
+++ b/inst/extdata/wb_projects_gov_sar.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -33,6 +33,12 @@
     <t xml:space="preserve">proj_approval_fy</t>
   </si>
   <si>
+    <t xml:space="preserve">asa_cn_approval_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">task_type</t>
+  </si>
+  <si>
     <t xml:space="preserve">proj_url</t>
   </si>
   <si>
@@ -82,6 +88,9 @@
   </si>
   <si>
     <t xml:space="preserve">Nepal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advisory</t>
   </si>
   <si>
     <t xml:space="preserve">https://opswork.worldbank.org/home/P513759</t>
@@ -103,7 +112,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -138,11 +149,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,18 +451,20 @@
     <col min="4" max="4" width="6.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="18.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="7.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="3.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="3.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,6 +521,12 @@
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -526,18 +546,20 @@
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="42.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="18.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="7.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -595,55 +617,65 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2028</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1" t="n">
-        <v>0</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>27</v>
+      <c r="R2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/wb_projects_gov_sar.xlsx
+++ b/inst/extdata/wb_projects_gov_sar.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t xml:space="preserve">theme_env_social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ida_cycle_approval</t>
   </si>
   <si>
     <t xml:space="preserve">comments</t>
@@ -464,7 +467,8 @@
     <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,6 +531,9 @@
       </c>
       <c r="T1" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -559,7 +566,8 @@
     <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -623,42 +631,45 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2028</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -674,8 +685,9 @@
       <c r="S2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>30</v>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/wb_projects_gov_sar.xlsx
+++ b/inst/extdata/wb_projects_gov_sar.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -33,7 +33,7 @@
     <t xml:space="preserve">proj_approval_fy</t>
   </si>
   <si>
-    <t xml:space="preserve">asa_cn_approval_date</t>
+    <t xml:space="preserve">asa_approval_date</t>
   </si>
   <si>
     <t xml:space="preserve">task_type</t>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tanuj Mathur (ADM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDA21</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -454,7 +457,7 @@
     <col min="4" max="4" width="6.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
@@ -553,7 +556,7 @@
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
@@ -654,7 +657,9 @@
       <c r="F2" s="1" t="n">
         <v>2028</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="1" t="n">
+        <v>45929</v>
+      </c>
       <c r="H2" s="1" t="s">
         <v>26</v>
       </c>
@@ -685,9 +690,11 @@
       <c r="S2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="1"/>
+      <c r="T2" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="U2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/wb_projects_gov_sar.xlsx
+++ b/inst/extdata/wb_projects_gov_sar.xlsx
@@ -655,7 +655,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>45929</v>

--- a/inst/extdata/wb_projects_gov_sar.xlsx
+++ b/inst/extdata/wb_projects_gov_sar.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -27,6 +27,9 @@
     <t xml:space="preserve">region</t>
   </si>
   <si>
+    <t xml:space="preserve">country_code</t>
+  </si>
+  <si>
     <t xml:space="preserve">country_name</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
   </si>
   <si>
     <t xml:space="preserve">South Asia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPL</t>
   </si>
   <si>
     <t xml:space="preserve">Nepal</t>
@@ -456,22 +462,23 @@
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="6.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="3.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="12.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="9.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="17.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="3.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="17.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="9.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="17.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="18.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="16.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="18.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +544,9 @@
       </c>
       <c r="U1" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -555,22 +565,23 @@
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="12.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="9.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="42.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="40.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="17.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="9.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="17.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="18.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="16.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="18.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -637,52 +648,55 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="H2" s="1" t="n">
         <v>45929</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O2" s="1"/>
-      <c r="P2" s="1" t="n">
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="Q2" s="1" t="n">
-        <v>0</v>
       </c>
       <c r="R2" s="1" t="n">
         <v>0</v>
@@ -690,11 +704,14 @@
       <c r="S2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>31</v>
+      <c r="T2" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
